--- a/users/test/Sandhata_Internship_Log.xlsx
+++ b/users/test/Sandhata_Internship_Log.xlsx
@@ -978,7 +978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1199,8 +1199,152 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WEEK 3</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>DAY 1</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>💻 Development: Implemented codebase features and visual upgrades.
+🤝 Team Sync: Attended daily meeting and aligned on milestones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Lunch Break</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Lunch Break</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="n"/>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="C8:C12"/>
     <mergeCell ref="C3:C7"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="B3:B7"/>
